--- a/data1.xlsx
+++ b/data1.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="20.28515625" customWidth="1" style="2" min="1" max="1"/>
@@ -2119,6 +2119,788 @@
         <v>0</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>55.31.015-001</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Полоса ручку КТ31 DN15</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Сталь 3</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Штаба 16х3</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K39" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>71.01.016-001</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Насадка на ручку DN15</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Поліетилен</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Порошок</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="K40" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="L40" t="n">
+        <v>45.84</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>41.31.015-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Патрубок корпуса 11с31п DN15х10</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Сталь 20</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Тр. 42.3х2.8</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="K41" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>42.01.015-001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Бобишка 11с31п DN15 (10x22)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Сталь 3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Круг 16</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="K42" t="n">
+        <v>190.08</v>
+      </c>
+      <c r="L42" t="n">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>53.01.004-002</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Штифт 4х9</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Сталь 45</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Круг калібр. 4</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K43" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>60.144</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>61.01.015-001</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Шток 11с31п DN15 (10x41)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Сталь 20Х13</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Круг 14</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="K44" t="n">
+        <v>281.52</v>
+      </c>
+      <c r="L44" t="n">
+        <v>109.331</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Сталь 20</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Труба 21.3х2.8</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="K45" t="n">
+        <v>211.68</v>
+      </c>
+      <c r="L45" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>50.01.015-001</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Втулка кріпильна DN15x10</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Сталь 08Х13</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Лист 0.8</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="K46" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="L46" t="n">
+        <v>99.023</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>51.01.015-001</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Пружина тарільчаста DN15x10</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Сталь 65Г</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Лист 0.8</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="K47" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="L47" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>52.01.015-001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Шайба DN15x10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Сталь 3</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Лист 1.5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="K48" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="L48" t="n">
+        <v>37.58</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Гайка М8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Гайка M8</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>11.31.015-001</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Кран 11с31п DN15x10</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="K50" t="n">
+        <v>760.3200000000001</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>60.01.015-001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Куля 21х10 Китай</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>70.04.015-001</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ущільнення штока DN15</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>72.01.007-001</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Гумове кільце 007-009-19</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>70.01.015-001</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ущільнення кулі 11с31п DN15x10</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>71.02.015-001</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Заглушка на патрубок. Кран 11с31п DN15х10</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Поліетилен</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Порошок</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="K55" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="L55" t="n">
+        <v>45.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.1968503937007874" right="0.07874015748031496" top="0.3937007874015748" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="landscape" paperSize="9" scale="72"/>
